--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4087,6 +4087,11 @@
           <t>฿822</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>done 2026-07-25 19:13</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4213,7 +4218,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99"]}</t>
+          <t>{"last_personas": ["F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3"], "recent_captions": ["ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4117,6 +4117,11 @@
           <t>฿175</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>done 2026-07-26 19:34</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4218,7 +4223,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3"], "recent_captions": ["ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822"]}</t>
+          <t>{"last_personas": ["F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4147,6 +4147,11 @@
           <t>฿3700</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>done 2026-07-27 20:46</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4223,7 +4228,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175"]}</t>
+          <t>{"last_personas": ["E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4177,6 +4177,11 @@
           <t>฿1451</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>done 2026-07-28 20:05</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4228,7 +4233,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700"]}</t>
+          <t>{"last_personas": ["E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก"], "last_roles": ["R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4207,6 +4207,11 @@
           <t>฿150</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>done 2026-07-29 20:12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4233,7 +4238,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก"], "last_roles": ["R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451"]}</t>
+          <t>{"last_personas": ["B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4210,6 +4210,1006 @@
       <c r="G143" t="inlineStr">
         <is>
           <t>done 2026-07-29 20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>37</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>น้ำมันถั่วเหลือง ตราองุ่น ขนาด1ลิตร แพ็ค3ขวด โปรโมชั่นสุดคุ้ม</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AbMVrSjRr</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztg-mnmyv5cdh05e5b.webp</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>฿182.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>38</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>The Chocolate Factory บราวนี่แครกเกอร์ แผ่นกลม รสดาร์กช็อกโกแลต ขนาด 40 กรัม</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VabKxlcAB</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztj-mlvtyt7kgburbc.webp</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>฿45.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>39</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ensure Gold AdvancePro wheat เอนชัวร์ โกลด์ แอดวานซ์โปร รสข้าวสาลี ขนาด 800 กรัม(1กระป๋อง)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdZZ95AAb</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mngva2okzpjaca.webp</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>฿690.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>40</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>[พร้อมส่งในไทย]Marukyu Koyamaen Matcha มัทฉะมารุคิวโคยามะเอ็น สาหร่ายผู้ดี อูมามิ เกรดพิธีการญี่ปุ่น</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pr3J5kKve</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasj-m91el64l52bt32.webp</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>฿1118.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>41</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>หมูสามชั้นแดดเดียวพรีเมี่ยม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง ไม่ใส่สารกันเสีย ทอดง่ายๆใน 5 นาที</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pjaUvq9ci</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mmfq4vxucrgla3.webp</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>฿189.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>42</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด 100% | SOURDOUGH BREAD |</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W4SZcVdkx</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>฿182.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>43</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>[ยกลัง12ขวด]น้ำมันปาล์ม มรกต และ ทับทิม ขวด 1ลิตร x 12 ขวด น้ำมันพืช มรกต และ ทับทิม</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BCgYgRq4z</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81zth-mmixuw8fz18i52.webp</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>฿893.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>44</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VwzlSdFG1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>฿1451.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>45</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Pre-order มาม่าJinmailang (จางหลิงเฮ่อ) แพค</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEy5OGUk8</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mni8oy7lbjer1f.webp</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>฿260.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>46</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>หอยจ๊อปูย่าเฮี๊ยะ (เกรดเนื้อหน้าอก)แถมฟรีน้ำจิ้มบ๊วย30ML</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATthiVwhF</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mncpondjeg3nd1.webp</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>฿270.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>47</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fmYj7nmUw</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>฿822.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>48</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>พร้อมส่งในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ มารุคิวของแท้จากญี่ปุ่น​ Matcha​ มัทฉะยี่ห้อดังจากอูจิ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6ff5uxshlo</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mn5j25gwgmx2ed.webp</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>฿790.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>49</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ปลาสลิดกรอบ ไร้ก้าง เต็มชิ้น กรอบอร่อย ไม่เหม็นหืน 🐟</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40eKk4DAW1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7qula-lhkogxzv71yba0.webp</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>฿150.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>50</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6ff5uyAZwu</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>฿149.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>51</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ไร่พระจันทร์ เมล็ดเจีย chia seed เมล็ดเชีย ธัญพืช มีอย. คัดพิเศษ เกรดพรีเมี่ยม</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9030hGB78j</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98u-lyj1u7grm8w1bb.webp</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>฿165.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>52</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>น้ำมันมรกต ขนาด 1 ลิตร สำหรับทำอาหาร แพ็ค 3 ขวด | น้ำมันพืชทำอาหาร ผัด ทอด อเนกประสงค์ ใช้ได้ทุกเมนู</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W4SZdljey</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztf-mm9msusd71fnbc.webp</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>฿280.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>53</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>เก๊กฮวยผงสำเร็จรูป HighlandHerb ขนาด 600 กรัม</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5DkXjty0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>฿249.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>54</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>สลิดติดปาก ปลาสลิดแดดเดียว 5-6 ตัว/โล | ปลาสลิดไข่บางบ่อ ตัวโต สด สะอาด เนื้อแน่นหอมมัน</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4fu1XIoEEN</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztm-mgvmi6civ40e0a.webp</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>฿469.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>55</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>นมกล่อง (ยกลัง) นมยูเอชที นมไฮคิวสูตร3 1พลัส ซูเปอร์โกลด์ รสจืด180 มล (27 กล่อง) นม UHT HiQ Super Gold UHT</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOdwr0WRj</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasg-m7hrtewsksjj0d.webp</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>฿669.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>56</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>เบอร์ทอลี่น้ำมันมะกอกเอ็กตร้าเวอร์จิน ขนาด500ml.</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9030hGnxIf</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mo16o8447m69aa.webp</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>฿560.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>57</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>พัดลมดูดอากาศติดฝ้า 8/10/12 นิ้ว แรงดูด 300CFM เงียบ ประหยัดไฟ พัดลมระบายอากาศห้องน้ำ รับประกัน 3 ปี</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaN0cYfkf</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-moysj4upxu6l2c.webp</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>฿479.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>58</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>MAILTANK เตาแก็ส IK03 เตาแก๊สหัวเดี่ยว เตาแก๊สพกพา ขนาดกะทัดรัด ไฟแรง ประหยัดแก๊ส พร้อมส่ง (ใช้กับหัวปรับแรงดันต่ำ)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AjMAaRBJL</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zth-mngmbtc89hc030.webp</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>฿229.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>59</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>พัดลมระบายอากาศ พัดลมระบายอากาศติดเพดาน 8 นิ้ว 12 นิ้ว ลมแรง เสียงเงียบ ประหยัดไฟ เหมาะกับห้องน้ำ ห้องครัว</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KvJYjR8jG</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zte-mohmysxqeeq7a2.webp</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>฿479.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>60</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>COD✅ ชั้นแม่เหล็กติดข้างตู้เย็น ชั้นวางแม่เหล็ก ไม่ต้องเจาะผนัง แรงดูดสูง รับน้ำหนักดี เหมาะสำหรับห้องครัว ห้องนอน และห้องน้ำ ประหยัดพื้นที่</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B5kb4pSRZ</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-821fp-mgndrxqlei2w9f.webp</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>฿44.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>61</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ชั้นวางแก้วไม้ไผ่ ชั้นวางแก้วน้ำ ชั้นวางจาน ทนทานต่อแรงกด ขนาดเล็กและประหยัดพื้นที่ อุปกรณ์จัดเก็บในครัว</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60PvyHnbm6</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-824gg-mpwi58v183d9f1.webp</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>฿45.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>62</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ถังขยะ ถังขยะแบบพกพา ถังขยะในครัว ดีไซน์มินิมอล แรงแบริ่งที่แข็งแกร่ง ประหยัดพื้นที่ ความจุขนาดใหญ่ แบบฝาสวิง</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zw4jdhFUM</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81zti-mhptex6zswsl5b.webp</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>฿48.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>63</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>แรงดันน้ําสูง 360° หัวก๊อกน้ําทองเหลือง สามโหมด ยืดหยุ่น ประหยัดน้ํา สําหรับอ่างล้างจาน ห้องครัว ในครัวเรือน</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qhponP5B0</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-7r98o-lmfyed9dgiqs57.webp</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>฿276.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>64</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>เครื่องปั่นไข่อเนกประสงค์ อุปกรณ์ตีไข่และผสมไข่ ใช้งานสะดวก เขย่าได้แรง ประหยัดเวลา เหมาะทำอาหารในครัว</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BS91ZaHZK</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-825zu-mjpf4xitpkaq0d.webp</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>฿89.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>65</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ปืนจุดแก๊ส ปืนจุดแก๊สใส่ถ่าน AA แบบสปาร์ค จุดติดง่ายไฟแรงทนทานประหยัด</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LHhzETDg9</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/a1b11015b4f86d5433baba12bd1f7e2b.webp</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>฿95.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>66</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>KUDSUN คีมแกะหอยแครง สแตนเลส ที่แกะหอยแครง อุปกรณ์แกะหอยทะเล ช่วยเปิดเปลือกหอยง่าย ประหยัดแรง ทำอาหาร ไม่เจ็บมือ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fY9xMPoJd</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-23020-kji2eakg95mv2a.webp</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>฿168.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>67</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ที่หนีบไม้กวาดแบบดูดติดผนัง ถ้วยดูดแรงสูง ไม่ต้องเจาะ ใช้แขวนไม้กวาดและที่ถูพื้นได้ ประหยัดพื้นที่ในห้องน้ำและห้องครัว</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VTfNNgVxy</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mlrhd1qtruh06f.webp</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>฿197.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>68</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>【พร้อมส่ง】หัวต่อก๊อกน้ำ 360° หมุนได้ ABS 3โหมด แรงดันสูง ประหยัดน้ำ ติดตั้งง่าย สำหรับอ่างล้างจานและห้องครัว</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qSuCU0hf9</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztq-mh06e1dr06j117.webp</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>฿17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>69</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>（COD）ก๊อกน้ำอ่างล้างจาน 4in1 หัวก๊อกครัว 4โหมด แรงดันสูง หมุนได้รอบทิศ สำหรับซิงค์ล้างจาน ติดตั้งง่าย ประหยัดน้ำ ล้างผัก</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V7Gwtmh0a</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-81ztg-migzx3z3d1j45e.webp</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>฿299.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>70</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>อุปกรณ์ครัว2โหมด360 หมุนได้ บับเบิ้ล แรงดันสูงก๊อกน้ํา ส่วนต่อขยาย ประหยัดน้ําห้องน้ําอุปกรณ์ครัวอุปกรณ์</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fJEL2r3Cr</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7ra3y-m52qjdz9ofmf74.webp</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>฿20.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>71</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ที่คั้นน้ำส้ม ที่บีบมะนาว 2in1 คั้นมือ+หมุนได้ในอุปกรณ์เดียว ประหยัดแรง</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KvJYl4x5Q</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/th-11134207-7rasd-m2m6flkttcwjb2.webp</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>฿109.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>72</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>หัวก๊อกน้ำเพิ่มแรงดัน แบบหมุนได้ 360 องศา เหมาะสำหรับใช้งานในห้องครัว หัวก๊อกน้ำฝักบัวประหยัดน้ำเพิ่มแรงดัน</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8Knqkb9fZa</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7rdyw-lzaaluuiprqicf.webp</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>฿28.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>73</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ก๊อกน้ำอ่างล้างจานแบบดึงออกสปริง360° อ่างล้างจานหมุนล้างจาน กะละมังผัก ก๊อกน้ำซิงค์ครัว หัวฉีดดึงได้ 2 หมุนรอบ 360° เพิ่มแรงดัน ประหยัดน้ำ ติดตั้งง่าย</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qDyaAVJOz</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-820l4-mjfr089l0s8x21.webp</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>฿699.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>74</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ก๊อกน้ําห้องครัวสากลกรองเครื่องกรองน้ําหัวฉีดในครัวเรือนแรงดันประหยัดน้ําสาดหลักฐานตาข่ายองค์ประกอบอะแดปเตอร์</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70ITA9RSni</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/cn-11134207-7ras8-m1nv75ekn12s34.webp</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>฿64.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>75</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ตะขอรางเลื่อนอเนกประสงค์ - 10 Gliding S-Hooks &amp; กาวเสริมแรง, ประหยัดพื้นที่ Organizer - สําหรับเครื่องมือครัว/หมวก Coats</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qaN0etnJT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-7rd5t-m7w0a1xbzp1t77.webp</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>฿33.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>76</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>【ปรับ 2 ระดับ/หมุน 360°】FM ก๊อกน้ำครัวแบบปรับแรงดันน้ำ หมุนได้รอบทิศทาง อุปกรณ์ประปาในบ้าน/ก๊อกน้ำปรับแรงดัน/ก๊อกน้ำห้องน้ำ/ก๊อกน้ำประหยัดน้ำ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qDyaArecr</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://down-tx-th.img.susercontent.com/sg-11134201-8262o-mlnangheu9z98f.webp</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>฿670.00</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4237,6 +4237,11 @@
           <t>฿182.00</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>done 2026-09-12 21:14</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5238,7 +5243,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150"]}</t>
+          <t>{"last_personas": ["F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5"], "recent_captions": ["โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4267,6 +4267,11 @@
           <t>฿45.00</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>done 2026-09-13 21:57</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5243,7 +5248,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E"], "last_hooks": ["โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5"], "recent_captions": ["โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00"]}</t>
+          <t>{"last_personas": ["H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4297,6 +4297,11 @@
           <t>฿690.00</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>done 2026-09-14 23:59</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5248,7 +5253,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00"]}</t>
+          <t>{"last_personas": ["A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1"], "recent_captions": ["อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4327,6 +4327,11 @@
           <t>฿1118.00</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>done 2026-09-15 22:37</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5253,7 +5258,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1"], "recent_captions": ["อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00"]}</t>
+          <t>{"last_personas": ["F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4357,6 +4357,11 @@
           <t>฿189.00</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>done 2026-09-16 22:27</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5258,7 +5263,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00"]}</t>
+          <t>{"last_personas": ["E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม"], "last_roles": ["R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4387,6 +4387,11 @@
           <t>฿182.00</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>done 2026-09-17 22:35</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5263,7 +5268,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม"], "last_roles": ["R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00"]}</t>
+          <t>{"last_personas": ["G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก"], "last_roles": ["R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2"], "recent_captions": ["ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4417,6 +4417,11 @@
           <t>฿893.00</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>done 2026-09-18 22:03</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5268,7 +5273,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก"], "last_roles": ["R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2"], "recent_captions": ["ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00"]}</t>
+          <t>{"last_personas": ["F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5245,6 +5245,106 @@
       <c r="F183" t="inlineStr">
         <is>
           <t>฿670.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>77</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>฿48,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>78</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A19 Pro หน้าจอ ProMotion 120Hz แบตเตอรี่อึดยิ่งขึ้น ระบบกล้องโปร เครื่องศูนย์แท้พร้อมประกันศูนย์ไทย</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>฿39,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>79</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) จอใหญ่เต็มตา แบตเตอรี่อึดทนทาน รองรับ Apple Intelligence เต็มรูปแบบ ชิป A18 เครื่องศูนย์ไทยแท้</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>฿34,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>80</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) พอร์ต USB-C กล้องหลัก 48MP หน้าจอ Dynamic Island คุ้มค่าที่สุดสำหรับรุ่นมาตรฐาน ใช้งานได้ยาวนาน</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>฿26,900.00</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5347,6 +5347,80 @@
           <t>฿26,900.00</t>
         </is>
       </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>81</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว ราคา 678.00 บาท</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qc9ZkOEib</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ลด 55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>82</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>JTL เครื่องปั่นน้ำผลไม้ สมูทตี้ มอเตอร์รอบสูงพิเศษ BD-388 ราคา 1590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KpdJo13zt</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcacyy53vboz1c.webp</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ลด 39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>83</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>(สินค้าขายดี) 1 ขวด ขวด1000g น้ำผึ้งโพรงป่าแท้เดือน5 Natural Honey ไม่ใช่ผึ้งฟาร์ม ไม่ผ่านความร้อน ไม่ผสม เก็บช่วงแล้ง ราคา 399.00 บาท</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VNz8UNscQ</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-824g3-mptu5ddu3w9acc.webp</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5272,6 +5272,11 @@
           <t>฿48,900.00</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>done 2026-09-19 21:31</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -5362,7 +5367,6 @@
           <t>https://s.shopee.co.th/1qc9ZkOEib</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
@@ -5388,7 +5392,6 @@
           <t>https://s.shopee.co.th/8KpdJo13zt</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcacyy53vboz1c.webp</t>
@@ -5414,13 +5417,11 @@
           <t>https://s.shopee.co.th/6VNz8UNscQ</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-824g3-mptu5ddu3w9acc.webp</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5447,7 +5448,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ..."], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00"]}</t>
+          <t>{"last_personas": ["B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3"], "recent_captions": ["เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4447,6 +4447,11 @@
           <t>฿1451.00</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>done 2026-09-20 21:44</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5448,7 +5453,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3"], "recent_captions": ["เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม"], "last_roles": ["R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5307,6 +5307,11 @@
           <t>฿39,900.00</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>done 2026-09-22 00:07</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -5453,7 +5458,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม"], "last_roles": ["R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4477,6 +4477,11 @@
           <t>฿260.00</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>done 2026-09-22 22:33</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5458,7 +5463,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C"], "last_hooks": ["โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5342,6 +5342,11 @@
           <t>฿34,900.00</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>done 2026-09-23 22:29</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -5463,7 +5468,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C"], "last_hooks": ["โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4507,6 +4507,11 @@
           <t>฿270.00</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>done 2026-09-24 22:51</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5468,7 +5473,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G", "A"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00", "กำลังหาของแบบนี้อยู่พอดี ส่วนตัวลองใช้แล้วประทับใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง หอยจ๊อปูย่าเฮี๊ยะ เกรดเนื้อหน้าอกแถมฟรีน้ำจิ้ ราคาแค่ 270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿270.00"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5377,6 +5377,11 @@
           <t>฿26,900.00</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>done 2026-09-25 22:51</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -5473,7 +5478,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G", "A"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00", "กำลังหาของแบบนี้อยู่พอดี ส่วนตัวลองใช้แล้วประทับใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง หอยจ๊อปูย่าเฮี๊ยะ เกรดเนื้อหน้าอกแถมฟรีน้ำจิ้ ราคาแค่ 270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿270.00"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G", "A", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6", "R4", "R2"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00", "กำลังหาของแบบนี้อยู่พอดี ส่วนตัวลองใช้แล้วประทับใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง หอยจ๊อปูย่าเฮี๊ยะ เกรดเนื้อหน้าอกแถมฟรีน้ำจิ้ ราคาแค่ 270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿270.00", "อันนี้เกินคาดจริงๆ ปกติเราเจอปัญหาพกสายชาร์จหลายแบบจนพันกันรกรุงรังในกระเป๋า แถมกล้องมือถือเดิมก็ไม่ชัด ถ่ายอะไรก็เบลอจนอึดอัดใจและเสียเวลาทำงานมากค่ะ จนเราได้สมาร์ทโฟน iPhone 15 ราคา 26,900 บาท เข้ามาช่วยชีวิต เพราะเปลี่ยนมาใช้พอร์ต USB-C ใช้สายร่วมกับอุปกรณ์อื่นได้ทันที พร้อมกล้อง 48MP ที่ถ่ายภาพได้คมชัดละเอียด ซึ่งการซื้อของราคาสูงแบบนี้เราเลือกสั่งจากร้านค้าทางการ Shopee Mall เพราะไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม อุ่นใจเรื่องของแท้และบริการหลังการขาย ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือกลัวโดนโกงเลยค่ะ ใครที่กำลังจะเปลี่ยนมือถือเซฟเก็บไว้ดูตอนช้อปกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿26,900.00"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4537,6 +4537,11 @@
           <t>฿822.00</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>done 2026-09-26 22:00</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5478,7 +5483,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G", "A", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6", "R4", "R2"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00", "กำลังหาของแบบนี้อยู่พอดี ส่วนตัวลองใช้แล้วประทับใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง หอยจ๊อปูย่าเฮี๊ยะ เกรดเนื้อหน้าอกแถมฟรีน้ำจิ้ ราคาแค่ 270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿270.00", "อันนี้เกินคาดจริงๆ ปกติเราเจอปัญหาพกสายชาร์จหลายแบบจนพันกันรกรุงรังในกระเป๋า แถมกล้องมือถือเดิมก็ไม่ชัด ถ่ายอะไรก็เบลอจนอึดอัดใจและเสียเวลาทำงานมากค่ะ จนเราได้สมาร์ทโฟน iPhone 15 ราคา 26,900 บาท เข้ามาช่วยชีวิต เพราะเปลี่ยนมาใช้พอร์ต USB-C ใช้สายร่วมกับอุปกรณ์อื่นได้ทันที พร้อมกล้อง 48MP ที่ถ่ายภาพได้คมชัดละเอียด ซึ่งการซื้อของราคาสูงแบบนี้เราเลือกสั่งจากร้านค้าทางการ Shopee Mall เพราะไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม อุ่นใจเรื่องของแท้และบริการหลังการขาย ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือกลัวโดนโกงเลยค่ะ ใครที่กำลังจะเปลี่ยนมือถือเซฟเก็บไว้ดูตอนช้อปกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿26,900.00"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H", "F", "H", "F", "E", "G", "E", "D", "H", "D", "E", "D", "E", "A", "C", "G", "C", "G", "A", "E", "G"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2", "R3", "R3", "R2", "R3", "R4", "R5", "R5", "R1", "R3", "R1", "R2", "R4", "R3", "R2", "R2", "R3", "R6", "R4", "R2", "R6"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99", "เห็นคนพูดถึงเยอะเลยลองกดสั่งน้ำมันพืชยกลังส่งตรงจากโรงงาน ขนาด 1 ลิตร x 12 ขวด ในราคา 822 บาทมาไว้เต็มบ้านเลยค่ะ\nมองไปทางไหนก็เจอแต่ขวดน้ำมัน นึกว่าเรากำลังจะเปิดร้านกล้วยทอดซะแล้ว 55555\nใครไม่อยากออกไปขนเอง เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822", "ไม่คิดว่าจะเจอน้ำพริกที่เข้ามาเปลี่ยนมื้ออาหารเดิมๆ ของครอบครัวเรา จากที่เมื่อก่อนมื้อเย็นที่บ้านน่าเบื่อมากจนทุกคนกินข้าวกันได้น้อยค่ะ พอได้ลองน้ำพริกหมูกระจก รสต้มยำ ที่ชิ้นใหญ่ เปรี้ยวเผ็ดสะใจ ตอนนี้คนที่บ้านเอนจอยกับการกินข้าวและเจริญอาหารขึ้นเยอะเลยค่ะ ตัวนี้มีขนาด 100g และ 400g ราคา 175 บาท ช่วยเปลี่ยนมื้อธรรมดาให้จัดจ้านถูกใจคนในบ้านมากๆ เซฟโพสต์เก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿175", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนหนูสุ่มดวงสั่งทุเรียนทีไรเจอแต่แข็งป๊กจนฟันแทบหักตลอดเลยค่ะ พอได้ลองทุเรียนหมอนทอง คัดพิเศษ ขนาด 3.5 กก. ลูกนี้คือฟินมาก เนื้อนุ่มกำลังดี ยกระดับลิ้นหนูจนไม่อยากกลับไปกินแบบเดิมอีก ถึงราคา 3700 บาท จะทำเอาเงินในบัญชีหนูแอบร้องไห้ แต่รสชาติเยียวยาจิตใจสุดๆ แชร์ต่อให้เพื่อนสาวกทุเรียนเซฟเก็บไว้กดสั่งตามกันได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿3700", "เมื่อวานเพิ่งเจอศึกหนักกับการทำงานจนสภาพเราเกือบกลายเป็นซอมบี้ สมองเบลอจนแทบจะวูบกลางอากาศค่ะ เลิกงานเลยต้องรีบกลับมาชงผงมัทฉะ รุ่น Aya no Mori ขนาด 20g/40g ซึ่งเป็นมัทฉะ Uji ส่งตรงจากญี่ปุ่น ดื่มแก้เหนื่อยสักหน่อย จิบแล้วกลิ่นชาเขียวมัทฉะหอมละมุนสมราคา 1451 บาท ช่วยกู้ชีวิตและสติของเรารับวันใหม่ได้พอดี สายชาเขียวลองเซฟเก็บไว้ดูตอนช้อป หรือกดแชร์ต่อให้เพื่อนที่เจอปัญหาทำงานหนักจนร่างพังเหมือนกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451", "มีใครเป็นเหมือนผมไหม ที่เคยสงสัยว่าน้ำปลาหวานเจ้าดังองค์พระปฐมเจดีย์จะอร่อยแตกต่างจากทั่วไปจริงไหม เพราะปกติเราซื้อกินที่ไหนก็เจอแต่น้ำตาลเชื่อมใสๆ ไม่ถูกปากสักที แต่พอตัดสินใจสั่งกระปุกละ 150 บาทมาลองจิ้มกับมะม่วงดิบดู ปรากฏว่ารสชาติเข้มข้นถึงเครื่องมากจนกลายเป็นของติดตู้เย็นที่ต้องมีไว้กินแก้ง่วงไปแล้วค่ะ ใครที่กำลังมองหาน้ำปลาหวานอร่อยๆ กินกับผลไม้เปรี้ยว เซฟโพสต์นี้ไว้หรือแชร์ต่อให้เพื่อนสายกินได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "ตอนแรกไม่ได้จะซื้อ แต่กำลังจะทำกับข้าวแล้วเปิดเจอว่าน้ำมันพืชหมดเกลี้ยงครัวเลยค่ะ เราเลยรีบกดสั่งน้ำมันถั่วเหลืองตราองุ่น ขนาด 1 ลิตร (แพ็ค 3) ราคา 182 บาท มาตุนไว้ทำอาหารรอบต่อไป ใครที่ต้องซื้อของใช้ในครัวเข้าบ้านอยู่เรื่อยๆ เซฟเก็บไว้ดูตอนช้อปได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "โดนป้ายยามาอีกที ช่วงบ่ายทีไรงานไม่ค่อยเดินเพราะปากเราเรียกร้องหาแต่ขนมกินเล่นตลอดเวลาค่ะ พอได้ลองบราวนี่แครกเกอร์ รสดาร์กช็อกโกแลต แผ่นกลม ขนาด 40 กรัม ราคา 45 บาท ซองนี้มาเคี้ยวเพลินๆ ตอนนั่งหน้าคอมก็ช่วยชีวิตคนหมดพลังแบบเราได้ตรงจุดเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿45.00", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเราเคยกังวลเรื่องโภชนาการของคนในครอบครัวมาก แต่ตอนนี้หมดห่วงเพราะมี นมผงสูตรครบถ้วน Gold AdvancePro รสข้าวสาลี ขนาด 800 กรัม ที่มีสารอาหารครบถ้วน ในราคา 690 บาทเข้ามาดูแลทุกคนค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้คนที่บ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿690.00", "อันนี้เกินคาดจริงๆ มีใครเคยเจอปัญหาอยากชงชาเขียวดื่มเองที่บ้านแล้วหารสชาติที่ถูกใจไม่เจอเหมือนเราบ้างไหมคะ? พอได้ลองผงมัทฉะที่เป็นเกรดพิธีการญี่ปุ่นกระปุกนี้ในราคา 1118 บาท คือได้รสอูมามิตามที่ตามหามานาน ตอบโจทย์คนที่อยากชงดื่มเองมากๆ ใครชอบมัทฉะแท้ๆ เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1118.00", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครเคยเหนื่อยจนไม่อยากยืนทำกับข้าวตอนเย็นเหมือนกันไหมคะ? วันก่อนเราเจอปัญหานี้เลยลองเอาหมูสามชั้นแดดเดียวที่ซื้อมาทำ ตัวนี้ผ่านการอบลมร้อน ไร้สารกันเสีย แถมทอดง่ายใน 5 นาทีก็ได้กินแล้ว ในราคา 189 บาท ใครอยากได้เมนูเร่งด่วนเซฟเก็บไว้ดูตอนคิดกับข้าวไม่ออก หรือแชร์ต่อให้เพื่อนที่กลับบ้านดึกบ่อยๆ ได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿189.00", "เห็นคนพูดถึงเยอะเลยลอง ปกติเราลองหัดทำขนมเองทีไรสภาพออกมาเหมือนก้อนถ่านทุกที มื้อเช้าเลยรอดชีวิตได้เพราะ ขนมปังซาวโดว์ แบบโฮมเมด 100% ราคา 182 บาท ชิ้นนี้นี่แหละค่ะ ใครชอบกินขนมปังแต่ขี้เกียจทำเองเหมือนเรา เซฟโพสต์เก็บไว้ดูตอนหาของกินได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿182.00", "ไม่คิดว่าจะ... ต้องมาเหนื่อยกับการวิ่งออกไปซื้อของเข้าครัวบ่อยขนาดนี้ เวลาจะทำกับข้าวทีไรแล้วเจอน้ำมันหมดกลางคันคือวุ่นวายมากค่ะ แต่ตอนนี้ชีวิตสบายขึ้นเยอะ มีของพร้อมใช้ทำอาหารตลอดไม่ต้องคอยพะวงอีกแล้ว เพราะเราสั่งน้ำมันปาล์มแบบขายยกลัง 12 ขวด ขนาด 1 ลิตร x 12 มาตุนไว้ติดบ้านในราคา 893 บาท ใครที่ทำกับข้าวทานเองบ่อยๆ เซฟเก็บไว้ดูตอนช้อปเข้าบ้านได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿893.00", "ลองแล้วเข้าใจเลยว่าทำไมขายดี มีใครกำลังเล็ง iPhone 18 Pro Max ที่มาพร้อมชิป A20 Pro อยู่เหมือนเราบ้างไหมคะ? สำหรับการซื้อมือถือราคาสูง 48,900 บาท เราว่าเลือกร้าน Mall ทางการใน Shopee Mall หรือ Apple Flagship Store อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เพราะไว้ใจร้านค้าได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกงค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿48,900.00", "เมื่อวานเพิ่งเจอ... มีใครกำลังตามหาผงมัทฉะอุจิ ส่งตรงจากญี่ปุ่น รุ่น Aya no Mori อยู่เหมือนเราไหมคะ? พอดีเราบังเอิญไปเจอช่วงจัดโปรโมชั่นลดราคาเหลือ 1451 บาท มีขนาด 20g/40g ให้เลือกด้วย เลยตื่นเต้นจนต้องรีบเอามาบอกต่อทุกคนค่ะ ใครที่เป็นสายชาเขียวมัทฉะกดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1451.00", "มีใครเป็นเหมือนผมไหม ที่ตอนแรกเราเคยสงสัยและไม่แน่ใจในคุณภาพว่าจะต่างจากเดิมไหม แถมกังวลเรื่องสั่งซื้อออนไลน์มาตลอด แต่พอตัดสินใจลองใช้ iPhone 17 Pro ราคา 39,900 บาท ชีวิตประจำวันก็สะดวกขึ้นชัดเจนด้วยความเร็วของชิป A19 Pro และจอ ProMotion 120Hz ที่ตอบสนองการใช้งานได้ทันใจ สิ่งที่เปลี่ยนความรู้สึกลังเลของหนูคือการไว้ใจร้านค้าได้ 100% เพราะเป็นร้านค้าทางการ Shopee Mall / Apple Flagship Store ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง ซึ่งการซื้อสมาร์ตโฟนราคาสูง เลือกร้าน Mall ทางการอุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด ใครที่กำลังหาข้อมูลอยู่เซฟเก็บไว้ดูตอนช้อปได้เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿39,900.00", "ตอนแรกไม่ได้จะซื้อ \n\nเมื่อก่อนเวลาดึกๆ เราหิวแล้วไม่มีอะไรกินติดห้องเลย แต่ตอนนี้แฮปปี้ขึ้นเยอะที่มีของกินตุนไว้ให้อุ่นใจค่ะ จุดเปลี่ยนคือเราบังเอิญไปเจอบะหมี่กึ่งสำเร็จรูป พรีออเดอร์ จางหลิงเฮ่อ แบบแพ็คในราคา 260 บาท แฟนคลับเซฟเก็บไว้ช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿260.00", "โดนป้ายยามาอีกที มีใครเคยลังเลเหมือนเราไหมคะว่ามือถือราคา 34,900 บาทอย่าง iPhone 16 Plus จะตอบโจทย์จริงหรือเปล่า? ตอนแรกหนูก็ไม่แน่ใจ แต่พอตัดสินใจซื้อมาลองใช้งานจริง ทั้งเรื่องจอใหญ่ แบตอึด และชิป A18 ก็ทำงานได้ลื่นไหลตามสเปกเลยค่ะ และสำหรับการซื้อสมาร์ตโฟนราคาสูงแบบนี้ เลือกร้านค้าทางการ Shopee Mall ทำให้เราไว้ใจร้านค้าได้ 100% ได้เครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมว เครื่องหิ้ว หรือกลัวโดนโกง อุ่นใจเรื่องของแท้และบริการหลังการขายที่สุด เซฟเก็บไว้ดูตอนช้อปกันได้นะคะ \n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿34,900.00", "กำลังหาของแบบนี้อยู่พอดี ส่วนตัวลองใช้แล้วประทับใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง หอยจ๊อปูย่าเฮี๊ยะ เกรดเนื้อหน้าอกแถมฟรีน้ำจิ้ ราคาแค่ 270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿270.00", "อันนี้เกินคาดจริงๆ ปกติเราเจอปัญหาพกสายชาร์จหลายแบบจนพันกันรกรุงรังในกระเป๋า แถมกล้องมือถือเดิมก็ไม่ชัด ถ่ายอะไรก็เบลอจนอึดอัดใจและเสียเวลาทำงานมากค่ะ จนเราได้สมาร์ทโฟน iPhone 15 ราคา 26,900 บาท เข้ามาช่วยชีวิต เพราะเปลี่ยนมาใช้พอร์ต USB-C ใช้สายร่วมกับอุปกรณ์อื่นได้ทันที พร้อมกล้อง 48MP ที่ถ่ายภาพได้คมชัดละเอียด ซึ่งการซื้อของราคาสูงแบบนี้เราเลือกสั่งจากร้านค้าทางการ Shopee Mall เพราะไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม อุ่นใจเรื่องของแท้และบริการหลังการขาย ไม่ต้องเสี่ยงกับเครื่องย้อมแมวหรือกลัวโดนโกงเลยค่ะ ใครที่กำลังจะเปลี่ยนมือถือเซฟเก็บไว้ดูตอนช้อปกันได้นะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿26,900.00", "แชร์เผื่อมีคนกำลังหาอยู่ ตอนแรกเราก็แอบไม่แน่ใจว่าจะโอเคไหมเพราะสั่งน้ำมันพืชส่งตรงจากโรงงานทางออนไลน์ แต่พอลองสั่งแบบยกลัง 12 ขวด ขนาด 1 ลิตร มาถึงบ้านในราคา 822 บาท สรุปคือได้ของเรียบร้อยปกติตามที่คิดไว้เลยค่ะ ใครที่กำลังมองหาน้ำมันพืชยกลังไปทำกับข้าว เซฟเก็บไว้ดูตอนช้อปได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿822.00"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4767,6 +4767,11 @@
           <t>฿560.00</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>done 2026-09-27T02:46:15.175319+00:00 live-graphics 554501167740603_122187046994726152</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
